--- a/valuation_template.xlsx
+++ b/valuation_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\PSX Trading\Research &amp; Workings\Shiny App Valuation Model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\PSX Trading\Research &amp; Workings\Valuation Model App\Streamlit app\Stock_valuation_engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB2F891-A69F-41C5-870C-B7FD22916E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4ADC95-61EB-48E9-8556-B7DC149EA4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Company" sheetId="5" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Market_data" sheetId="2" r:id="rId3"/>
     <sheet name="Industry_data" sheetId="3" r:id="rId4"/>
     <sheet name="Valuation_weights" sheetId="4" r:id="rId5"/>
+    <sheet name="Instructions" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>Year</t>
   </si>
@@ -168,17 +169,57 @@
   </si>
   <si>
     <t>Weight</t>
+  </si>
+  <si>
+    <t>All financial data and shares outstanding number should be in millions.</t>
+  </si>
+  <si>
+    <t>Strictly follow the template format. Use % where values are in percentage.</t>
+  </si>
+  <si>
+    <t>Industry_average</t>
+  </si>
+  <si>
+    <t>Workings Table</t>
+  </si>
+  <si>
+    <t>Change values in shaded area only</t>
+  </si>
+  <si>
+    <t>Change values in shaded area only.</t>
+  </si>
+  <si>
+    <t>Weights need not to be changed. Keep them as they are. However, if you prefer some other weightage you can change.</t>
+  </si>
+  <si>
+    <t>Important Notes</t>
+  </si>
+  <si>
+    <t>Financial_data Sheet</t>
+  </si>
+  <si>
+    <t>Market_data Sheet</t>
+  </si>
+  <si>
+    <t>Industry_data Sheet</t>
+  </si>
+  <si>
+    <t>Valuation_weights Sheet</t>
+  </si>
+  <si>
+    <t>Table below is for your own working. Calculate industry average in table below and then enter the averages in shaded are on Industry_data sheet.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.000000%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,13 +242,45 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -224,7 +297,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -233,36 +306,65 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -273,6 +375,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7CBA18DF-FEA5-4178-91FE-E9DC33D725E7}" name="Table1" displayName="Table1" ref="A13:D19" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A13:D19" xr:uid="{7CBA18DF-FEA5-4178-91FE-E9DC33D725E7}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{F7ADD530-9148-4CB0-A47B-D28FF6D6E1D6}" name="Company"/>
+    <tableColumn id="2" xr3:uid="{383949F3-A88D-45E0-A75E-EF44C787C5F5}" name="PE"/>
+    <tableColumn id="3" xr3:uid="{E3F2AC04-1465-45DA-80BB-08A4D5B34B44}" name="PS"/>
+    <tableColumn id="4" xr3:uid="{847330C7-95EF-4A3E-A5A6-5DED440534C1}" name="EV_EBITDA"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -554,10 +669,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -616,167 +731,167 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+      <c r="A2" s="9">
         <v>2021</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="15">
         <v>114345</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="15">
         <v>52646</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="16">
         <v>39865</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="15">
         <v>3769.4</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="15">
         <v>12706.3</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="16">
         <v>25647</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="15">
         <f>19172+6954+38999</f>
         <v>65125</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="16">
         <v>133250</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="9">
         <v>1272.2</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+      <c r="A3" s="9">
         <v>2022</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="15">
         <v>125678</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="15">
         <v>56559</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="16">
         <v>34370</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="15">
         <v>5050</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="15">
         <v>-3299.6</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="16">
         <v>9688</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="15">
         <f>17821+6703+58813</f>
         <v>83337</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="16">
         <v>134732</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="9">
         <v>1272.2</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+      <c r="A4" s="9">
         <v>2023</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="15">
         <v>181382</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="15">
         <v>81114</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="16">
         <v>47452</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="15">
         <v>5325</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="15">
         <v>11898.7</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="16">
         <v>12053</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="15">
         <f>19565+6544+15133</f>
         <v>41242</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="16">
         <v>186207</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="9">
         <v>1272.2</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+      <c r="A5" s="9">
         <v>2024</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="15">
         <v>411254</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="15">
         <v>150792</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="16">
         <v>85525</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="15">
         <v>7470.4</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="15">
         <v>14986</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="16">
         <v>66467</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="15">
         <f>32491+7418+38341</f>
         <v>78250</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="16">
         <v>324679</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="9">
         <v>1423.1</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+      <c r="A6" s="9">
         <v>2025</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="15">
         <v>483808</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="15">
         <v>143417</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="16">
         <v>84946</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="15">
         <v>10073</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="15">
         <v>13193</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="16">
         <v>69962</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="15">
         <f>50818+11637+22010</f>
         <v>84465</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="16">
         <v>337214</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="9">
         <v>1423.1</v>
       </c>
     </row>
@@ -788,14 +903,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14C56AB6-8FF8-473C-A65F-856D363841DA}">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -803,76 +919,77 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="9">
         <v>560.74</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="10">
         <v>10.29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="6">
-        <f>Industry_data!C2</f>
+      <c r="B4" s="10">
+        <f>Instructions!C14</f>
         <v>1.72</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="2">
-        <f>Industry_data!D2</f>
+      <c r="B5" s="9">
+        <f>Instructions!D14</f>
         <v>7.23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="2">
-        <f>Industry_data!B7</f>
+      <c r="B6" s="9">
+        <f>Instructions!B19</f>
         <v>12.14</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2">
-        <f>Industry_data!C7</f>
+      <c r="B7" s="9">
+        <f>Instructions!C19</f>
         <v>1.5449999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2">
-        <f>Industry_data!D7</f>
+      <c r="B8" s="9">
+        <f>Instructions!D19</f>
         <v>6.5449999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="11">
         <v>0.115</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -881,43 +998,43 @@
         <v>6.6600000000000006E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="9">
         <v>0.93</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="13">
         <v>0.16</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="9">
+      <c r="B13" s="13">
         <v>0.37</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="14">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B15" s="9">
+      <c r="B15" s="13">
         <v>0.03</v>
       </c>
     </row>
@@ -928,17 +1045,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C37AA49D-2B4C-4BEF-B22E-2AAA53064336}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.08984375" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
-        <v>21</v>
+      <c r="A1" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>22</v>
@@ -952,92 +1069,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>10.29</v>
-      </c>
-      <c r="C2">
-        <v>1.72</v>
-      </c>
-      <c r="D2">
-        <v>7.23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3">
-        <v>12.53</v>
-      </c>
-      <c r="C3">
-        <v>2.19</v>
-      </c>
-      <c r="D3">
-        <v>5.86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4">
-        <v>11.75</v>
-      </c>
-      <c r="C4">
-        <v>1.37</v>
-      </c>
-      <c r="D4">
-        <v>5.84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5">
-        <v>13.79</v>
-      </c>
-      <c r="C5">
-        <v>0.82</v>
-      </c>
-      <c r="D5">
-        <v>14.05</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3">
-        <f>AVERAGE(B2:B5)</f>
-        <v>12.09</v>
-      </c>
-      <c r="C6" s="3">
-        <f>AVERAGE(C2:C5)</f>
-        <v>1.5250000000000001</v>
-      </c>
-      <c r="D6" s="3">
-        <f>AVERAGE(D2:D5)</f>
-        <v>8.245000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="3">
-        <f>MEDIAN(B2:B5)</f>
+        <v>45</v>
+      </c>
+      <c r="B2" s="8">
         <v>12.14</v>
       </c>
-      <c r="C7" s="3">
-        <f>MEDIAN(C2:C5)</f>
-        <v>1.5449999999999999</v>
-      </c>
-      <c r="D7" s="3">
-        <f>MEDIAN(D2:D5)</f>
-        <v>6.5449999999999999</v>
+      <c r="C2" s="8">
+        <v>1.54</v>
+      </c>
+      <c r="D2" s="8">
+        <v>6.54</v>
       </c>
     </row>
   </sheetData>
@@ -1066,7 +1107,7 @@
       <c r="A2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="17">
         <v>0.5</v>
       </c>
     </row>
@@ -1074,7 +1115,7 @@
       <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="17">
         <v>0.2</v>
       </c>
     </row>
@@ -1082,7 +1123,7 @@
       <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="17">
         <v>0.1</v>
       </c>
     </row>
@@ -1090,11 +1131,207 @@
       <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="17">
         <v>0.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907CB5B0-D47C-461E-BE39-109AD36F42DF}">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.36328125" customWidth="1"/>
+    <col min="4" max="4" width="12.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="19"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="19"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="7">
+        <v>10.29</v>
+      </c>
+      <c r="C14" s="7">
+        <v>1.72</v>
+      </c>
+      <c r="D14" s="7">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="7">
+        <v>12.53</v>
+      </c>
+      <c r="C15" s="7">
+        <v>2.19</v>
+      </c>
+      <c r="D15" s="7">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="7">
+        <v>11.75</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1.37</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="7">
+        <v>13.79</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.82</v>
+      </c>
+      <c r="D17" s="7">
+        <v>14.05</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="3">
+        <f>AVERAGE(B14:B17)</f>
+        <v>12.09</v>
+      </c>
+      <c r="C18" s="3">
+        <f>AVERAGE(C14:C17)</f>
+        <v>1.5250000000000001</v>
+      </c>
+      <c r="D18" s="3">
+        <f>AVERAGE(D14:D17)</f>
+        <v>8.245000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="3">
+        <f>MEDIAN(B14:B17)</f>
+        <v>12.14</v>
+      </c>
+      <c r="C19" s="3">
+        <f>MEDIAN(C14:C17)</f>
+        <v>1.5449999999999999</v>
+      </c>
+      <c r="D19" s="3">
+        <f>MEDIAN(D14:D17)</f>
+        <v>6.5449999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="19"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/valuation_template.xlsx
+++ b/valuation_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\PSX Trading\Research &amp; Workings\Valuation Model App\Streamlit app\Stock_valuation_engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC4ADC95-61EB-48E9-8556-B7DC149EA4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D615FA-0158-45C5-9736-E8BF24AEBD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>Year</t>
   </si>
@@ -75,24 +75,6 @@
     <t>Current Market Price</t>
   </si>
   <si>
-    <t>Current PE</t>
-  </si>
-  <si>
-    <t>Current PS</t>
-  </si>
-  <si>
-    <t>Current EV/EBITDA</t>
-  </si>
-  <si>
-    <t>Industry PE</t>
-  </si>
-  <si>
-    <t>Industry PS</t>
-  </si>
-  <si>
-    <t>Industry EV/EBITDA</t>
-  </si>
-  <si>
     <t>Risk Free Rate</t>
   </si>
   <si>
@@ -192,9 +174,6 @@
     <t>Weights need not to be changed. Keep them as they are. However, if you prefer some other weightage you can change.</t>
   </si>
   <si>
-    <t>Important Notes</t>
-  </si>
-  <si>
     <t>Financial_data Sheet</t>
   </si>
   <si>
@@ -207,19 +186,49 @@
     <t>Valuation_weights Sheet</t>
   </si>
   <si>
-    <t>Table below is for your own working. Calculate industry average in table below and then enter the averages in shaded are on Industry_data sheet.</t>
+    <t>Important Instructions</t>
+  </si>
+  <si>
+    <t>Only change data in grey shaded cells. DO NOT ADD EVEN A SINGLE DOT IN ANY OTHER CELL OTHERWISE THE VALUATION APP WON'T WORK.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Table below is for your own working. Calculate industry average in table below and then enter the averages in shaded are on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Industry_data</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sheet.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.000000%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,6 +252,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
@@ -278,7 +325,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FF002060"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -297,7 +344,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -309,14 +356,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -338,7 +381,10 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -669,10 +715,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
     </row>
@@ -709,189 +755,189 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+      <c r="A2" s="8">
         <v>2021</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="13">
         <v>114345</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="13">
         <v>52646</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="14">
         <v>39865</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="13">
         <v>3769.4</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="13">
         <v>12706.3</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="14">
         <v>25647</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="13">
         <f>19172+6954+38999</f>
         <v>65125</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="14">
         <v>133250</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="8">
         <v>1272.2</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>2022</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="13">
         <v>125678</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="13">
         <v>56559</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="14">
         <v>34370</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="13">
         <v>5050</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="13">
         <v>-3299.6</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="14">
         <v>9688</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="13">
         <f>17821+6703+58813</f>
         <v>83337</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="14">
         <v>134732</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="8">
         <v>1272.2</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2023</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="13">
         <v>181382</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="13">
         <v>81114</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="14">
         <v>47452</v>
       </c>
-      <c r="E4" s="15">
+      <c r="E4" s="13">
         <v>5325</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="13">
         <v>11898.7</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="14">
         <v>12053</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="13">
         <f>19565+6544+15133</f>
         <v>41242</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="14">
         <v>186207</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <v>1272.2</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>2024</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="13">
         <v>411254</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="13">
         <v>150792</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="14">
         <v>85525</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="13">
         <v>7470.4</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="13">
         <v>14986</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="14">
         <v>66467</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="13">
         <f>32491+7418+38341</f>
         <v>78250</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="14">
         <v>324679</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>1423.1</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>2025</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="13">
         <v>483808</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="13">
         <v>143417</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="14">
         <v>84946</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="13">
         <v>10073</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="13">
         <v>13193</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="14">
         <v>69962</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="13">
         <f>50818+11637+22010</f>
         <v>84465</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="14">
         <v>337214</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>1423.1</v>
       </c>
     </row>
@@ -903,7 +949,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14C56AB6-8FF8-473C-A65F-856D363841DA}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -911,7 +957,7 @@
     <col min="8" max="8" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -919,122 +965,68 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>560.74</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="10">
-        <v>10.29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B3" s="9">
+        <v>0.115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="10">
-        <f>Instructions!C14</f>
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <f>18.16%-B3</f>
+        <v>6.6600000000000006E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="9">
-        <f>Instructions!D14</f>
-        <v>7.23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B5" s="8">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="9">
-        <f>Instructions!B19</f>
-        <v>12.14</v>
-      </c>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B6" s="11">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="9">
-        <f>Instructions!C19</f>
-        <v>1.5449999999999999</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="B7" s="11">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="9">
-        <f>Instructions!D19</f>
-        <v>6.5449999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="B8" s="12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B9" s="11">
-        <v>0.115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="12">
-        <f>18.16%-B9</f>
-        <v>6.6600000000000006E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="9">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="13">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="13">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="13">
         <v>0.03</v>
       </c>
     </row>
@@ -1058,26 +1050,26 @@
         <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="8">
+        <v>39</v>
+      </c>
+      <c r="B2" s="7">
         <v>12.14</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>1.54</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>6.54</v>
       </c>
     </row>
@@ -1097,41 +1089,41 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="17">
+        <v>27</v>
+      </c>
+      <c r="B2" s="15">
         <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="17">
+        <v>16</v>
+      </c>
+      <c r="B3" s="15">
         <v>0.2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="17">
+        <v>17</v>
+      </c>
+      <c r="B4" s="15">
         <v>0.1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="17">
+        <v>18</v>
+      </c>
+      <c r="B5" s="15">
         <v>0.2</v>
       </c>
     </row>
@@ -1142,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{907CB5B0-D47C-461E-BE39-109AD36F42DF}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.36328125" customWidth="1"/>
@@ -1150,136 +1142,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="19"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="20"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="17"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="17"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="17"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3" s="19"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="19"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="19"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" t="s">
-        <v>55</v>
-      </c>
-    </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>48</v>
+      <c r="A11" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="6">
+        <v>10.29</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1.72</v>
+      </c>
+      <c r="D14" s="6">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="6">
+        <v>12.53</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2.19</v>
+      </c>
+      <c r="D15" s="6">
+        <v>5.86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="6">
+        <v>11.75</v>
+      </c>
+      <c r="C16" s="6">
+        <v>1.37</v>
+      </c>
+      <c r="D16" s="6">
+        <v>5.84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="7">
-        <v>10.29</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1.72</v>
-      </c>
-      <c r="D14" s="7">
-        <v>7.23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="7">
-        <v>12.53</v>
-      </c>
-      <c r="C15" s="7">
-        <v>2.19</v>
-      </c>
-      <c r="D15" s="7">
-        <v>5.86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="7">
-        <v>11.75</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1.37</v>
-      </c>
-      <c r="D16" s="7">
-        <v>5.84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>13.79</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>0.82</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>14.05</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B18" s="3">
         <f>AVERAGE(B14:B17)</f>
@@ -1296,7 +1295,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
         <f>MEDIAN(B14:B17)</f>
@@ -1311,20 +1310,20 @@
         <v>6.5449999999999999</v>
       </c>
     </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="17"/>
+    </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="19"/>
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="6" t="s">
-        <v>49</v>
+      <c r="A22" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/valuation_template.xlsx
+++ b/valuation_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\PSX Trading\Research &amp; Workings\Valuation Model App\Streamlit app\Stock_valuation_engine\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D615FA-0158-45C5-9736-E8BF24AEBD9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{628EA293-5350-4C8D-BF43-7E7A6B05928A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
